--- a/results/link-prediction-gcn/Link/5shot/IMDB-BINARY/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/5shot/IMDB-BINARY/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4818±0.0000</t>
+          <t>0.4816±0.0003</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5198±0.0012</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5240±0.0078</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0002</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5181±0.0000</t>
+          <t>0.5816±0.0038</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4818±0.0000</t>
+          <t>0.4816±0.0003</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5226±0.0031</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5235±0.0066</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5185±0.0003</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5125±0.0000</t>
+          <t>0.5705±0.0178</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4818±0.0000</t>
+          <t>0.4816±0.0003</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5276±0.0047</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5257±0.0019</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5181±0.0004</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5185±0.0004</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5185±0.0003</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5183±0.0003</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5183±0.0003</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5183±0.0003</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0002</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5392±0.0106</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.5843±0.0000</t>
+          <t>0.5753±0.0020</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0003</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5195±0.0009</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5151±0.0045</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5100±0.0000</t>
+          <t>0.5023±0.0120</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5133±0.0000</t>
+          <t>0.5030±0.0116</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5104±0.0000</t>
+          <t>0.5180±0.0011</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5048±0.0000</t>
+          <t>0.5091±0.0133</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5048±0.0000</t>
+          <t>0.5091±0.0133</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5048±0.0000</t>
+          <t>0.5091±0.0133</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.4989±0.0138</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.5905±0.0000</t>
+          <t>0.5921±0.0068</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5106±0.0089</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4818±0.0000</t>
+          <t>0.4483±0.0471</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5567±0.0000</t>
+          <t>0.5353±0.0192</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5180±0.0005</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0002</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0002</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0002</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0002</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5537±0.0000</t>
+          <t>0.5959±0.0035</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5146±0.0035</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.4818±0.0000</t>
+          <t>0.4816±0.0003</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5290±0.0063</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5196±0.0000</t>
+          <t>0.5199±0.0006</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0004</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5183±0.0003</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5183±0.0002</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5185±0.0004</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5185±0.0004</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5185±0.0004</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5184±0.0003</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5308±0.0156</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5185±0.0003</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.5412±0.0000</t>
+          <t>0.5041±0.0252</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5177±0.0013</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5197±0.0000</t>
+          <t>0.5229±0.0032</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5159±0.0022</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5100±0.0118</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5184±0.0000</t>
+          <t>0.5186±0.0004</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5148±0.0050</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5183±0.0003</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5304±0.0000</t>
+          <t>0.5970±0.0098</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5181±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0004</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6839±0.0022</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0002</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0002</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0002</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6825±0.0000</t>
+          <t>0.6948±0.0019</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0003</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,62 +1425,62 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0009</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6838±0.0020</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.6759±0.0000</t>
+          <t>0.6915±0.0068</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1490,322 +1490,322 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6838±0.0028</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.6829±0.0000</t>
+          <t>0.6844±0.0005</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6824±0.0004</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0002</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0002</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0002</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6794±0.0029</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.3846±0.0000</t>
+          <t>0.3517±0.0107</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.6825±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0001</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.6826±0.0000</t>
+          <t>0.6797±0.0042</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.6752±0.0000</t>
+          <t>0.6668±0.0117</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.6781±0.0000</t>
+          <t>0.6672±0.0118</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.6754±0.0000</t>
+          <t>0.6823±0.0010</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.6704±0.0000</t>
+          <t>0.6736±0.0129</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.6704±0.0000</t>
+          <t>0.6736±0.0129</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.6704±0.0000</t>
+          <t>0.6736±0.0129</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.6825±0.0000</t>
+          <t>0.6630±0.0140</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.7050±0.0000</t>
+          <t>0.7023±0.0019</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.6821±0.0000</t>
+          <t>0.6727±0.0116</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
+          <t>0.1720±0.2432</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6869±0.0049</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6825±0.0005</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6828±0.0002</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6828±0.0002</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6828±0.0002</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6828±0.0002</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6966±0.0008</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6767±0.0065</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6965±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6805±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6845±0.0024</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.6832±0.0000</t>
+          <t>0.6830±0.0003</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0003</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0002</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0003</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6784±0.0046</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.2306±0.0000</t>
+          <t>0.0871±0.0981</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6822±0.0011</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6829±0.0000</t>
+          <t>0.6826±0.0011</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6802±0.0000</t>
+          <t>0.6802±0.0025</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6826±0.0000</t>
+          <t>0.6746±0.0114</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6794±0.0048</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6826±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6826±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6826±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6825±0.0000</t>
+          <t>0.6827±0.0003</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6872±0.0000</t>
+          <t>0.7125±0.0031</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6826±0.0000</t>
+          <t>0.6828±0.0001</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.3301±0.0000</t>
+          <t>0.3369±0.0034</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7233±0.0019</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6645±0.0000</t>
+          <t>0.7293±0.0101</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6991±0.0000</t>
+          <t>0.7416±0.0231</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.7222±0.0000</t>
+          <t>0.7269±0.0030</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7227±0.0000</t>
+          <t>0.7276±0.0031</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.7233±0.0000</t>
+          <t>0.7278±0.0029</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7229±0.0000</t>
+          <t>0.7327±0.0017</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7229±0.0000</t>
+          <t>0.7327±0.0017</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7229±0.0000</t>
+          <t>0.7327±0.0017</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.7223±0.0000</t>
+          <t>0.7276±0.0021</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.7060±0.0000</t>
+          <t>0.7294±0.0026</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7189±0.0000</t>
+          <t>0.7370±0.0011</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.3301±0.0000</t>
+          <t>0.3372±0.0035</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7233±0.0000</t>
+          <t>0.7279±0.0028</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.6707±0.0000</t>
+          <t>0.7038±0.0191</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.7093±0.0000</t>
+          <t>0.7078±0.0165</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.7249±0.0000</t>
+          <t>0.7429±0.0005</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.7242±0.0000</t>
+          <t>0.7404±0.0023</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7211±0.0000</t>
+          <t>0.7267±0.0014</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7426±0.0014</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7426±0.0014</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7426±0.0014</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.7228±0.0000</t>
+          <t>0.7331±0.0042</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7201±0.0000</t>
+          <t>0.7309±0.0031</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7206±0.0000</t>
+          <t>0.7409±0.0040</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.3305±0.0000</t>
+          <t>0.3374±0.0033</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.7228±0.0000</t>
+          <t>0.7239±0.0016</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6650±0.0000</t>
+          <t>0.6909±0.0046</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.7060±0.0000</t>
+          <t>0.7312±0.0085</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.7228±0.0000</t>
+          <t>0.7553±0.0023</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.7226±0.0000</t>
+          <t>0.7568±0.0032</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.7228±0.0000</t>
+          <t>0.7288±0.0024</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.7554±0.0031</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.7554±0.0031</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.7554±0.0031</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.7223±0.0000</t>
+          <t>0.7280±0.0022</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.7002±0.0000</t>
+          <t>0.7229±0.0020</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7193±0.0000</t>
+          <t>0.7629±0.0020</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6743±0.0000</t>
+          <t>0.6975±0.0126</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7237±0.0000</t>
+          <t>0.7184±0.0023</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.6680±0.0000</t>
+          <t>0.7292±0.0313</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.7083±0.0000</t>
+          <t>0.7042±0.0064</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.7129±0.0000</t>
+          <t>0.7183±0.0081</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.7184±0.0000</t>
+          <t>0.7181±0.0105</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.6995±0.0000</t>
+          <t>0.7158±0.0024</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.7165±0.0000</t>
+          <t>0.7114±0.0083</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.7165±0.0000</t>
+          <t>0.7114±0.0083</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.7165±0.0000</t>
+          <t>0.7114±0.0083</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.7410±0.0000</t>
+          <t>0.7203±0.0045</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.7553±0.0000</t>
+          <t>0.7452±0.0041</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.7201±0.0000</t>
+          <t>0.7337±0.0069</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.3307±0.0000</t>
+          <t>0.3376±0.0031</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.7216±0.0000</t>
+          <t>0.7237±0.0017</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.7267±0.0000</t>
+          <t>0.7465±0.0164</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.7187±0.0000</t>
+          <t>0.7388±0.0102</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.7225±0.0000</t>
+          <t>0.7238±0.0022</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.7229±0.0000</t>
+          <t>0.7235±0.0019</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.7226±0.0000</t>
+          <t>0.7237±0.0021</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.7229±0.0000</t>
+          <t>0.7237±0.0020</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.7229±0.0000</t>
+          <t>0.7237±0.0020</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.7229±0.0000</t>
+          <t>0.7237±0.0020</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.7223±0.0000</t>
+          <t>0.7243±0.0025</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7137±0.0000</t>
+          <t>0.7265±0.0008</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.7251±0.0054</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.3304±0.0000</t>
+          <t>0.3371±0.0035</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7241±0.0020</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.6620±0.0000</t>
+          <t>0.7019±0.0205</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6997±0.0000</t>
+          <t>0.7309±0.0114</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.7225±0.0000</t>
+          <t>0.7382±0.0064</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7406±0.0049</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7299±0.0034</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.7216±0.0000</t>
+          <t>0.7358±0.0062</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.7216±0.0000</t>
+          <t>0.7358±0.0062</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.7216±0.0000</t>
+          <t>0.7358±0.0062</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.7226±0.0000</t>
+          <t>0.7284±0.0019</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6846±0.0000</t>
+          <t>0.7203±0.0072</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.7192±0.0000</t>
+          <t>0.7391±0.0021</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.6887±0.0000</t>
+          <t>0.7060±0.0078</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7083±0.0000</t>
+          <t>0.7236±0.0014</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.7006±0.0000</t>
+          <t>0.7128±0.0375</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.7132±0.0000</t>
+          <t>0.7080±0.0024</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.7281±0.0000</t>
+          <t>0.7264±0.0145</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.7406±0.0000</t>
+          <t>0.7217±0.0212</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7043±0.0000</t>
+          <t>0.7294±0.0033</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7372±0.0000</t>
+          <t>0.7242±0.0046</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7372±0.0000</t>
+          <t>0.7242±0.0046</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7372±0.0000</t>
+          <t>0.7242±0.0046</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7016±0.0000</t>
+          <t>0.7260±0.0061</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7693±0.0000</t>
+          <t>0.7667±0.0010</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7496±0.0000</t>
+          <t>0.7597±0.0002</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.4382±0.0000</t>
+          <t>0.4462±0.0040</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7445±0.0000</t>
+          <t>0.7471±0.0023</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.6560±0.0000</t>
+          <t>0.7497±0.0089</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6941±0.0000</t>
+          <t>0.7588±0.0144</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.7436±0.0000</t>
+          <t>0.7503±0.0032</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7452±0.0000</t>
+          <t>0.7482±0.0020</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7449±0.0000</t>
+          <t>0.7488±0.0031</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7457±0.0000</t>
+          <t>0.7480±0.0020</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7457±0.0000</t>
+          <t>0.7480±0.0020</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7457±0.0000</t>
+          <t>0.7480±0.0020</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.7454±0.0000</t>
+          <t>0.7464±0.0027</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7076±0.0000</t>
+          <t>0.7285±0.0013</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7357±0.0000</t>
+          <t>0.7467±0.0003</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.4382±0.0000</t>
+          <t>0.4469±0.0040</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7426±0.0000</t>
+          <t>0.7342±0.0085</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6807±0.0000</t>
+          <t>0.7344±0.0179</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7161±0.0000</t>
+          <t>0.7375±0.0127</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7534±0.0022</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.7548±0.0012</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7472±0.0000</t>
+          <t>0.7477±0.0035</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.7531±0.0017</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.7531±0.0017</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.7531±0.0017</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.7496±0.0032</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7191±0.0000</t>
+          <t>0.7279±0.0036</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7390±0.0000</t>
+          <t>0.7482±0.0044</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.4389±0.0000</t>
+          <t>0.4471±0.0037</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.7453±0.0000</t>
+          <t>0.7461±0.0007</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6646±0.0000</t>
+          <t>0.7260±0.0068</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6993±0.0000</t>
+          <t>0.7516±0.0036</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7435±0.0000</t>
+          <t>0.7617±0.0008</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.7623±0.0025</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.7441±0.0000</t>
+          <t>0.7466±0.0021</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7631±0.0011</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7631±0.0011</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7631±0.0011</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.7434±0.0000</t>
+          <t>0.7485±0.0035</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.7027±0.0000</t>
+          <t>0.7215±0.0030</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.7390±0.0000</t>
+          <t>0.7602±0.0024</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7158±0.0000</t>
+          <t>0.7272±0.0060</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7459±0.0000</t>
+          <t>0.7439±0.0019</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.6930±0.0000</t>
+          <t>0.7492±0.0189</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.7306±0.0000</t>
+          <t>0.7356±0.0042</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.7420±0.0000</t>
+          <t>0.7547±0.0042</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7458±0.0000</t>
+          <t>0.7551±0.0045</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.7364±0.0000</t>
+          <t>0.7506±0.0074</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7473±0.0000</t>
+          <t>0.7504±0.0056</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7473±0.0000</t>
+          <t>0.7504±0.0056</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7473±0.0000</t>
+          <t>0.7504±0.0056</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.7517±0.0000</t>
+          <t>0.7517±0.0054</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7457±0.0000</t>
+          <t>0.7363±0.0067</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.7427±0.0000</t>
+          <t>0.7559±0.0030</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.4394±0.0000</t>
+          <t>0.4476±0.0036</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7387±0.0000</t>
+          <t>0.7451±0.0016</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.7490±0.0000</t>
+          <t>0.7662±0.0175</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7406±0.0000</t>
+          <t>0.7523±0.0070</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7439±0.0000</t>
+          <t>0.7465±0.0022</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7465±0.0024</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.7469±0.0024</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.7450±0.0000</t>
+          <t>0.7465±0.0024</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.7450±0.0000</t>
+          <t>0.7465±0.0024</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.7450±0.0000</t>
+          <t>0.7465±0.0024</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7472±0.0000</t>
+          <t>0.7472±0.0026</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7192±0.0000</t>
+          <t>0.7282±0.0015</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7387±0.0000</t>
+          <t>0.7440±0.0080</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.4387±0.0000</t>
+          <t>0.4465±0.0039</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7447±0.0000</t>
+          <t>0.7462±0.0015</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6579±0.0000</t>
+          <t>0.7338±0.0194</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.7308±0.0000</t>
+          <t>0.7519±0.0087</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7451±0.0000</t>
+          <t>0.7526±0.0035</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7526±0.0029</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7467±0.0000</t>
+          <t>0.7508±0.0029</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7446±0.0000</t>
+          <t>0.7504±0.0038</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7446±0.0000</t>
+          <t>0.7504±0.0038</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7446±0.0000</t>
+          <t>0.7504±0.0038</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7441±0.0000</t>
+          <t>0.7483±0.0015</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.6936±0.0000</t>
+          <t>0.7188±0.0042</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7369±0.0000</t>
+          <t>0.7469±0.0025</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7300±0.0023</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7460±0.0000</t>
+          <t>0.7348±0.0037</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.6979±0.0000</t>
+          <t>0.7385±0.0241</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.7367±0.0000</t>
+          <t>0.7337±0.0018</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.7474±0.0000</t>
+          <t>0.7527±0.0040</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.7550±0.0000</t>
+          <t>0.7517±0.0059</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7449±0.0000</t>
+          <t>0.7521±0.0031</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7536±0.0000</t>
+          <t>0.7491±0.0015</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7536±0.0000</t>
+          <t>0.7491±0.0015</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7536±0.0000</t>
+          <t>0.7491±0.0015</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7385±0.0000</t>
+          <t>0.7508±0.0040</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7523±0.0000</t>
+          <t>0.7490±0.0034</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7519±0.0000</t>
+          <t>0.7588±0.0015</t>
         </is>
       </c>
     </row>
